--- a/data/trans_bre/IQ2608_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ2608_R3-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,23%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 2,41</t>
+          <t>-17,38; 1,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 4,26</t>
+          <t>-7,3; 5,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 5,68</t>
+          <t>-11,85; 4,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 14,08</t>
+          <t>-17,31; 17,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 2,93</t>
+          <t>-20,25; 1,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 4,75</t>
+          <t>-7,69; 6,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 7,24</t>
+          <t>-13,85; 5,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 16,67</t>
+          <t>-18,12; 21,65</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,57%</t>
+          <t>-3,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 5,02</t>
+          <t>-8,34; 5,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 5,39</t>
+          <t>-4,16; 5,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 7,0</t>
+          <t>-3,29; 6,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 16,34</t>
+          <t>-18,77; 14,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 7,72</t>
+          <t>-11,72; 8,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 6,39</t>
+          <t>-4,66; 6,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 8,32</t>
+          <t>-3,7; 8,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 26,0</t>
+          <t>-24,76; 21,67</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,26</t>
+          <t>-9,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-10,54%</t>
+          <t>-13,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,67; -5,03</t>
+          <t>-23,78; -2,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 11,09</t>
+          <t>-3,71; 11,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 5,42</t>
+          <t>-8,17; 5,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 13,62</t>
+          <t>-25,74; 10,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,32; -8,16</t>
+          <t>-36,95; -6,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 15,81</t>
+          <t>-4,97; 17,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 7,11</t>
+          <t>-9,94; 6,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 23,12</t>
+          <t>-34,5; 17,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-5,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-9,29%</t>
+          <t>-8,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 13,42</t>
+          <t>-2,63; 13,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 0,63</t>
+          <t>-14,49; 1,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,32; -1,6</t>
+          <t>-16,44; -1,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 9,65</t>
+          <t>-20,68; 10,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 29,57</t>
+          <t>-5,18; 30,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 0,85</t>
+          <t>-18,61; 1,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,21; -2,06</t>
+          <t>-19,54; -1,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 17,04</t>
+          <t>-30,58; 20,47</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-4,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,72%</t>
+          <t>-6,6%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,13</t>
+          <t>-7,08; 1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,17</t>
+          <t>-4,14; 2,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,6</t>
+          <t>-6,31; 0,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 4,82</t>
+          <t>-13,67; 5,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 1,76</t>
+          <t>-10,84; 1,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 2,67</t>
+          <t>-4,98; 3,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 0,68</t>
+          <t>-7,37; 0,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 7,66</t>
+          <t>-18,85; 7,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2608_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ2608_R3-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-7,92</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,46</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-9,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-4,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-7.917976469908316</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.233026926538583</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.459783023782403</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.4199945089362056</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.09527367163439973</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.01346327322601382</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.04219764144093319</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.004593758614895619</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-17,38; 1,6</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,3; 5,29</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-11,85; 4,09</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-17,31; 17,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-20,25; 1,86</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-7,69; 6,03</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-13,85; 5,15</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-18,12; 21,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-17.38065816773997</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.296263360725136</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-11.85456580012037</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-17.31472063461337</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2024612844885306</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.07689996660665499</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1384543795553047</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1811782536699486</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.602562768618777</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.286667400773711</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.094586343431893</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>17.40736439553674</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.01856891480025863</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.06033940371657653</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.05149096724369507</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.216497486200829</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-2,21%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-3,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,34; 5,41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 5,12</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,29; 6,72</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-18,77; 14,47</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-11,72; 8,04</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-4,66; 6,14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-3,7; 8,1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-24,76; 21,67</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.503563418824483</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6854295426037771</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.017208824458361</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.605618973088208</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.02206693425571555</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.007892341979040736</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.02332830959614794</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.03607922066562083</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-14,28</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,43</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-9,31</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-22,98%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-13,49%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.343527437915952</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.159956878097283</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.29177510717565</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-18.77369656923261</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1172271665406122</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.04658200870043644</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.03697302531878237</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2476174306847818</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-23,78; -2,9</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,71; 11,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,17; 5,24</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-25,74; 10,28</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-36,95; -6,31</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-4,97; 17,2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-9,94; 6,75</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-34,5; 17,18</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.405987346464332</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.121331547674627</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.724643074970683</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>14.47179060605764</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.08040141782568472</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.06140865461505931</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.08100324301575031</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2167167817228814</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-6,98</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-8,9</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-9,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-10,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-8,02%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-14.28291955989026</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.428477342508485</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.073992350849651</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-9.312688649908852</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2298028152283235</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.04638563673817856</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.01336910610592273</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.134946257648241</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 13,73</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-14,49; 1,09</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-16,44; -1,44</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-20,68; 10,6</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-5,18; 30,85</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-18,61; 1,35</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-19,54; -1,96</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-30,58; 20,47</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-23.7803071181643</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.713481443580804</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.173481412590181</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-25.73718707195433</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.369523059082313</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.04972345201732119</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.09941397805333249</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3450109599773287</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-2.897800982327502</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.96452872310111</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.241443271150515</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.27519394105858</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.0631220047741396</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1720181265085738</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.06749096377014629</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1718197866071827</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5.441005590852066</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-6.984453216403763</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-8.899425172891096</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-5.008789217849108</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1114372924011719</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.09323588388967666</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1079230795787837</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.08024069798362392</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.631814444090273</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-14.49058543630112</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-16.44072776864423</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-20.68083643093473</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.05176841744186272</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1861035116976313</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1953554010061975</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3057800164336671</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>13.73014048744872</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.087740013118216</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-1.439776408214548</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>10.59964698581584</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3084812914985429</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.01345221265011285</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-0.01955777798961021</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2047271916856734</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,97</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,19%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-3,29%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-6,6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-7,08; 1,02</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,14; 2,62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,31; 0,31</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,67; 5,01</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-10,84; 1,64</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; 3,26</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-7,37; 0,37</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-18,85; 7,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.972954968622632</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.9735269749811315</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.735871521137989</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-4.515526901115996</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.04677686431450846</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.01189578354559187</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.03286502019176372</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.06604070738185348</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-7.081845135924332</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.144298430373778</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.305370556775001</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-13.66710817466211</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1083550283610847</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.04977966437748108</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.07373131052137642</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.188474352558203</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.018790818862799</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.618742798529417</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3104098169418997</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.008386819733057</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.0164088958388643</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.03263715462530749</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.003651554403977374</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.07910177876466264</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
